--- a/verification/model_verification_results_57_buses_raw.xlsx
+++ b/verification/model_verification_results_57_buses_raw.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\verification\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087ED870-0093-4345-A2EA-F82561815216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>checkpoint_57_25_False_vr_vi_final.pt_0.00</t>
   </si>
@@ -145,16 +139,34 @@
     <t>Vm Up Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Up Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Up Avg Violation</t>
+  </si>
+  <si>
     <t>Vm Down Max Violation</t>
   </si>
   <si>
     <t>Vm Down Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Down Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Down Avg Violation</t>
+  </si>
+  <si>
     <t>Vm tot Max Violation</t>
   </si>
   <si>
     <t>Vm tot Avg Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Avg Violation</t>
   </si>
   <si>
     <t>Ibal tot Max Violation</t>
@@ -166,8 +178,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,21 +242,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -282,7 +286,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -316,7 +320,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -351,10 +354,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,22 +529,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="38.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="40.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="0" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="39.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="0" hidden="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Y29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -619,30 +610,30 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B2">
-        <v>2040707.625</v>
+        <v>1999999.75</v>
       </c>
       <c r="C2">
-        <v>2022310.625</v>
+        <v>2000009.25</v>
       </c>
       <c r="D2">
-        <v>2006578.125</v>
+        <v>1999716.25</v>
       </c>
       <c r="E2">
-        <v>2002227</v>
+        <v>1999480.5</v>
       </c>
       <c r="F2">
-        <v>2000047.75</v>
+        <v>1999352.375</v>
       </c>
       <c r="G2">
-        <v>1999284.75</v>
+        <v>1999281.25</v>
       </c>
       <c r="H2">
-        <v>1.2028980255126951</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -660,66 +651,66 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>16.532438278198239</v>
+        <v>15.37712669372559</v>
       </c>
       <c r="O2">
-        <v>12.89453792572021</v>
+        <v>12.21967220306396</v>
       </c>
       <c r="P2">
-        <v>9.8545417785644531</v>
+        <v>9.615761756896973</v>
       </c>
       <c r="Q2">
-        <v>8.2625465393066406</v>
+        <v>8.230090141296387</v>
       </c>
       <c r="R2">
-        <v>7.4452672004699707</v>
+        <v>7.434841632843018</v>
       </c>
       <c r="S2">
-        <v>6.8801398277282706</v>
+        <v>6.880139827728271</v>
       </c>
       <c r="T2">
-        <v>9.8526849746704102</v>
+        <v>9.584171295166016</v>
       </c>
       <c r="U2">
-        <v>8.7054252624511719</v>
+        <v>8.704327583312988</v>
       </c>
       <c r="V2">
-        <v>8.1408195495605469</v>
+        <v>8.140223503112793</v>
       </c>
       <c r="W2">
-        <v>7.6667046546936044</v>
+        <v>7.666530132293701</v>
       </c>
       <c r="X2">
-        <v>7.2497153282165527</v>
+        <v>7.249697208404541</v>
       </c>
       <c r="Y2">
-        <v>6.8752660751342773</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+        <v>6.875266075134277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B3">
-        <v>2000982.625</v>
+        <v>1999356.625</v>
       </c>
       <c r="C3">
-        <v>2000050.75</v>
+        <v>1998659.125</v>
       </c>
       <c r="D3">
-        <v>1999339.75</v>
+        <v>1997902.375</v>
       </c>
       <c r="E3">
-        <v>1998957.25</v>
+        <v>1997314.625</v>
       </c>
       <c r="F3">
-        <v>1998802.375</v>
+        <v>1996980.375</v>
       </c>
       <c r="G3">
-        <v>1998712.25</v>
+        <v>1996745.625</v>
       </c>
       <c r="H3">
-        <v>2.1103473380208019E-2</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -737,602 +728,602 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.3809232711791992</v>
+        <v>2.064881563186646</v>
       </c>
       <c r="O3">
-        <v>1.6105431318283081</v>
+        <v>1.434581995010376</v>
       </c>
       <c r="P3">
-        <v>1.032563328742981</v>
+        <v>0.9767890572547913</v>
       </c>
       <c r="Q3">
-        <v>0.77588587999343872</v>
+        <v>0.7578251361846924</v>
       </c>
       <c r="R3">
-        <v>0.64417433738708496</v>
+        <v>0.6395490169525146</v>
       </c>
       <c r="S3">
-        <v>0.57697534561157227</v>
+        <v>0.5769748091697693</v>
       </c>
       <c r="T3">
-        <v>1.0211164951324461</v>
+        <v>0.9818696975708008</v>
       </c>
       <c r="U3">
-        <v>0.83902353048324585</v>
+        <v>0.8356943726539612</v>
       </c>
       <c r="V3">
-        <v>0.74414551258087158</v>
+        <v>0.7439846396446228</v>
       </c>
       <c r="W3">
-        <v>0.6682475209236145</v>
+        <v>0.6682267189025879</v>
       </c>
       <c r="X3">
-        <v>0.61845916509628296</v>
+        <v>0.6184571385383606</v>
       </c>
       <c r="Y3">
         <v>0.5762704610824585</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B4">
-        <v>2038807.625</v>
+        <v>1999902.5</v>
       </c>
       <c r="C4">
-        <v>2020361.875</v>
+        <v>1999187.875</v>
       </c>
       <c r="D4">
-        <v>2009653.5</v>
+        <v>1998845.625</v>
       </c>
       <c r="E4">
-        <v>2001911.125</v>
+        <v>1998593.375</v>
       </c>
       <c r="F4">
-        <v>2000569.625</v>
+        <v>1998464.5</v>
       </c>
       <c r="G4">
-        <v>1999880.875</v>
+        <v>1998391.25</v>
       </c>
       <c r="H4">
-        <v>24.101009368896481</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>18.897182464599609</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>17.383358001708981</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>16.459415435791019</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>15.789493560791019</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>15.217350006103519</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>6.2150087356567383</v>
+        <v>4.16663932800293</v>
       </c>
       <c r="O4">
-        <v>3.3941302299499512</v>
+        <v>2.693041324615479</v>
       </c>
       <c r="P4">
-        <v>1.6174309253692629</v>
+        <v>1.383974432945251</v>
       </c>
       <c r="Q4">
-        <v>0.54338639974594116</v>
+        <v>0.4997604489326477</v>
       </c>
       <c r="R4">
-        <v>0.1193082332611084</v>
+        <v>0.1155604124069214</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="T4">
-        <v>1.1077671051025391</v>
+        <v>0.9952500462532043</v>
       </c>
       <c r="U4">
-        <v>0.64858496189117432</v>
+        <v>0.6089640855789185</v>
       </c>
       <c r="V4">
-        <v>0.62016081809997559</v>
+        <v>0.3991452157497406</v>
       </c>
       <c r="W4">
-        <v>0.35051584243774409</v>
+        <v>0.2327483296394348</v>
       </c>
       <c r="X4">
-        <v>0.114506721496582</v>
+        <v>0.08177506923675537</v>
       </c>
       <c r="Y4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B5">
-        <v>2000908.375</v>
+        <v>1999067</v>
       </c>
       <c r="C5">
-        <v>2000051.875</v>
+        <v>1998243.125</v>
       </c>
       <c r="D5">
-        <v>1999481.625</v>
+        <v>1997440.5</v>
       </c>
       <c r="E5">
-        <v>1999113.25</v>
+        <v>1996785.625</v>
       </c>
       <c r="F5">
-        <v>1998952.25</v>
+        <v>1996434.875</v>
       </c>
       <c r="G5">
-        <v>1998844.25</v>
+        <v>1996186.375</v>
       </c>
       <c r="H5">
-        <v>0.73274630308151245</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.5169411301612854</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.41842710971832281</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0.36311474442481989</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0.32684800028800959</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.3019675612449646</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.115303754806519</v>
+        <v>1.239311099052429</v>
       </c>
       <c r="O5">
-        <v>0.87219983339309692</v>
+        <v>0.4933177530765533</v>
       </c>
       <c r="P5">
-        <v>0.34407007694244379</v>
+        <v>0.2585084438323975</v>
       </c>
       <c r="Q5">
-        <v>0.1068473756313324</v>
+        <v>0.08978640288114548</v>
       </c>
       <c r="R5">
-        <v>1.988470554351807E-2</v>
+        <v>0.01926006935536861</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0.25173977017402649</v>
+        <v>0.2102902978658676</v>
       </c>
       <c r="U5">
-        <v>0.1396363228559494</v>
+        <v>0.1298189908266068</v>
       </c>
       <c r="V5">
-        <v>0.1073347106575966</v>
+        <v>0.07049701362848282</v>
       </c>
       <c r="W5">
-        <v>5.8419305831193917E-2</v>
+        <v>0.03879138827323914</v>
       </c>
       <c r="X5">
-        <v>1.9084453582763668E-2</v>
+        <v>0.01362917851656675</v>
       </c>
       <c r="Y5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B6">
-        <v>2040707.625</v>
+        <v>1999999.75</v>
       </c>
       <c r="C6">
-        <v>2022310.625</v>
+        <v>2000009.25</v>
       </c>
       <c r="D6">
-        <v>2009653.5</v>
+        <v>1999716.25</v>
       </c>
       <c r="E6">
-        <v>2002227</v>
+        <v>1999480.5</v>
       </c>
       <c r="F6">
-        <v>2000569.625</v>
+        <v>1999352.375</v>
       </c>
       <c r="G6">
-        <v>1999880.875</v>
+        <v>1999281.25</v>
       </c>
       <c r="H6">
-        <v>24.101009368896481</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>18.897182464599609</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>17.383358001708981</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>16.459415435791019</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>15.789493560791019</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>15.217350006103519</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>16.532438278198239</v>
+        <v>15.37712669372559</v>
       </c>
       <c r="O6">
-        <v>12.89453792572021</v>
+        <v>12.21967220306396</v>
       </c>
       <c r="P6">
-        <v>9.8545417785644531</v>
+        <v>9.615761756896973</v>
       </c>
       <c r="Q6">
-        <v>8.2625465393066406</v>
+        <v>8.230090141296387</v>
       </c>
       <c r="R6">
-        <v>7.4452672004699707</v>
+        <v>7.434841632843018</v>
       </c>
       <c r="S6">
-        <v>6.8801398277282706</v>
+        <v>6.880139827728271</v>
       </c>
       <c r="T6">
-        <v>9.8526849746704102</v>
+        <v>9.584171295166016</v>
       </c>
       <c r="U6">
-        <v>8.7054252624511719</v>
+        <v>8.704327583312988</v>
       </c>
       <c r="V6">
-        <v>8.1408195495605469</v>
+        <v>8.140223503112793</v>
       </c>
       <c r="W6">
-        <v>7.6667046546936044</v>
+        <v>7.666530132293701</v>
       </c>
       <c r="X6">
-        <v>7.2497153282165527</v>
+        <v>7.249697208404541</v>
       </c>
       <c r="Y6">
-        <v>6.8752660751342773</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+        <v>6.875266075134277</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B7">
-        <v>2000945.25</v>
+        <v>1999211.875</v>
       </c>
       <c r="C7">
-        <v>2000051.375</v>
+        <v>1998451.125</v>
       </c>
       <c r="D7">
-        <v>1999410.75</v>
+        <v>1997671.375</v>
       </c>
       <c r="E7">
-        <v>1999035.25</v>
+        <v>1997050.125</v>
       </c>
       <c r="F7">
-        <v>1998877.375</v>
+        <v>1996707.625</v>
       </c>
       <c r="G7">
-        <v>1998778.25</v>
+        <v>1996466</v>
       </c>
       <c r="H7">
-        <v>0.37692490220069891</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.2584705650806427</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.2092135697603226</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.18155737221241</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0.16342400014400479</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0.1509837806224823</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>2.3145184516906738</v>
+        <v>1.858489036560059</v>
       </c>
       <c r="O7">
-        <v>1.4259573221206669</v>
+        <v>1.199265956878662</v>
       </c>
       <c r="P7">
-        <v>0.86044001579284668</v>
+        <v>0.7972187995910645</v>
       </c>
       <c r="Q7">
-        <v>0.60862630605697632</v>
+        <v>0.5908154845237732</v>
       </c>
       <c r="R7">
-        <v>0.48810195922851563</v>
+        <v>0.4844768047332764</v>
       </c>
       <c r="S7">
-        <v>0.4327315092086792</v>
+        <v>0.4327311217784882</v>
       </c>
       <c r="T7">
-        <v>0.82877230644226074</v>
+        <v>0.7889748215675354</v>
       </c>
       <c r="U7">
-        <v>0.66417676210403442</v>
+        <v>0.6592255234718323</v>
       </c>
       <c r="V7">
-        <v>0.58494281768798828</v>
+        <v>0.5756127238273621</v>
       </c>
       <c r="W7">
-        <v>0.51579046249389648</v>
+        <v>0.5108678936958313</v>
       </c>
       <c r="X7">
-        <v>0.46861553192138672</v>
+        <v>0.4672501385211945</v>
       </c>
       <c r="Y7">
-        <v>0.43220284581184393</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.4322028458118439</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B8">
-        <v>50331.9375</v>
+        <v>1637.271728515625</v>
       </c>
       <c r="C8">
-        <v>28195.783203125</v>
+        <v>1432.278564453125</v>
       </c>
       <c r="D8">
-        <v>13799.970703125</v>
+        <v>1134.428955078125</v>
       </c>
       <c r="E8">
-        <v>6173.58203125</v>
+        <v>870.9774169921875</v>
       </c>
       <c r="F8">
-        <v>2468.98291015625</v>
+        <v>784.3131713867188</v>
       </c>
       <c r="G8">
-        <v>1004.341003417969</v>
+        <v>721.5611572265625</v>
       </c>
       <c r="H8">
-        <v>23.158235549926761</v>
+        <v>2.668367624282837</v>
       </c>
       <c r="I8">
-        <v>18.367599487304691</v>
+        <v>2.374656915664673</v>
       </c>
       <c r="J8">
-        <v>15.07388114929199</v>
+        <v>2.140704870223999</v>
       </c>
       <c r="K8">
-        <v>13.326398849487299</v>
+        <v>1.946276426315308</v>
       </c>
       <c r="L8">
-        <v>12.2292537689209</v>
+        <v>1.76574444770813</v>
       </c>
       <c r="M8">
-        <v>11.56190872192383</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.599138498306274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>3163.8857421875</v>
+        <v>879.480224609375</v>
       </c>
       <c r="C9">
-        <v>2148.314697265625</v>
+        <v>637.4147338867188</v>
       </c>
       <c r="D9">
-        <v>1473.887084960938</v>
+        <v>398.1282653808594</v>
       </c>
       <c r="E9">
-        <v>1086.347900390625</v>
+        <v>290.3258056640625</v>
       </c>
       <c r="F9">
-        <v>908.34808349609375</v>
+        <v>261.4377136230469</v>
       </c>
       <c r="G9">
-        <v>821.1903076171875</v>
+        <v>240.5203857421875</v>
       </c>
       <c r="H9">
-        <v>0.8246304988861084</v>
+        <v>0.8982505798339844</v>
       </c>
       <c r="I9">
-        <v>0.64800053834915161</v>
+        <v>0.7915523052215576</v>
       </c>
       <c r="J9">
-        <v>0.5587916374206543</v>
+        <v>0.7135682702064514</v>
       </c>
       <c r="K9">
-        <v>0.50925040245056152</v>
+        <v>0.6487588286399841</v>
       </c>
       <c r="L9">
-        <v>0.47625294327735901</v>
+        <v>0.5885815024375916</v>
       </c>
       <c r="M9">
-        <v>0.45318865776062012</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.5330461859703064</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B10">
-        <v>49526.34375</v>
+        <v>1262.382568359375</v>
       </c>
       <c r="C10">
-        <v>27856.978515625</v>
+        <v>1107.089599609375</v>
       </c>
       <c r="D10">
-        <v>13497.724609375</v>
+        <v>860.0577392578125</v>
       </c>
       <c r="E10">
-        <v>5514.89111328125</v>
+        <v>608.5933837890625</v>
       </c>
       <c r="F10">
-        <v>2125.15966796875</v>
+        <v>481.2086791992188</v>
       </c>
       <c r="G10">
-        <v>1051.61962890625</v>
+        <v>406.85888671875</v>
       </c>
       <c r="H10">
-        <v>12.48301792144775</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>10.704019546508791</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>10.20773506164551</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>10.067220687866209</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>9.9699764251708984</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>9.8937702178955078</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B11">
-        <v>3235.32861328125</v>
+        <v>420.794189453125</v>
       </c>
       <c r="C11">
-        <v>2186.90625</v>
+        <v>369.0298767089844</v>
       </c>
       <c r="D11">
-        <v>1492.56201171875</v>
+        <v>286.6859130859375</v>
       </c>
       <c r="E11">
-        <v>1096.226196289062</v>
+        <v>202.8644561767578</v>
       </c>
       <c r="F11">
-        <v>917.85589599609375</v>
+        <v>160.4028930664062</v>
       </c>
       <c r="G11">
-        <v>836.264404296875</v>
+        <v>135.61962890625</v>
       </c>
       <c r="H11">
-        <v>0.59670168161392212</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.50822573900222778</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.46478280425071722</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>0.44247445464134222</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>0.42790058255195618</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0.41887295246124268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B12">
-        <v>50331.9375</v>
+        <v>1637.271728515625</v>
       </c>
       <c r="C12">
-        <v>28195.783203125</v>
+        <v>1432.278564453125</v>
       </c>
       <c r="D12">
-        <v>13799.970703125</v>
+        <v>1134.428955078125</v>
       </c>
       <c r="E12">
-        <v>6173.58203125</v>
+        <v>870.9774169921875</v>
       </c>
       <c r="F12">
-        <v>2468.98291015625</v>
+        <v>784.3131713867188</v>
       </c>
       <c r="G12">
-        <v>1051.61962890625</v>
+        <v>721.5611572265625</v>
       </c>
       <c r="H12">
-        <v>23.158235549926761</v>
+        <v>2.668367624282837</v>
       </c>
       <c r="I12">
-        <v>18.367599487304691</v>
+        <v>2.374656915664673</v>
       </c>
       <c r="J12">
-        <v>15.07388114929199</v>
+        <v>2.140704870223999</v>
       </c>
       <c r="K12">
-        <v>13.326398849487299</v>
+        <v>1.946276426315308</v>
       </c>
       <c r="L12">
-        <v>12.2292537689209</v>
+        <v>1.76574444770813</v>
       </c>
       <c r="M12">
-        <v>11.56190872192383</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.599138498306274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B13">
-        <v>3199.607421875</v>
+        <v>650.13720703125</v>
       </c>
       <c r="C13">
-        <v>2167.6103515625</v>
+        <v>503.2222900390625</v>
       </c>
       <c r="D13">
-        <v>1483.224487304688</v>
+        <v>342.4070739746094</v>
       </c>
       <c r="E13">
-        <v>1091.286987304688</v>
+        <v>246.5951385498047</v>
       </c>
       <c r="F13">
-        <v>913.10198974609375</v>
+        <v>210.9203033447266</v>
       </c>
       <c r="G13">
-        <v>828.727294921875</v>
+        <v>188.0700073242188</v>
       </c>
       <c r="H13">
-        <v>0.71066612005233765</v>
+        <v>0.4491252899169922</v>
       </c>
       <c r="I13">
-        <v>0.5781131386756897</v>
+        <v>0.3957761526107788</v>
       </c>
       <c r="J13">
-        <v>0.51178717613220215</v>
+        <v>0.3567841351032257</v>
       </c>
       <c r="K13">
-        <v>0.47586241364479059</v>
+        <v>0.3243794143199921</v>
       </c>
       <c r="L13">
-        <v>0.45207679271697998</v>
+        <v>0.2942907512187958</v>
       </c>
       <c r="M13">
-        <v>0.43603077530860901</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.2665230929851532</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B14">
-        <v>7.7674245834350586</v>
+        <v>7.767424583435059</v>
       </c>
       <c r="C14">
         <v>0.7780301570892334</v>
@@ -1350,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>5.9378385543823242E-2</v>
+        <v>0.05937838554382324</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1368,15 +1359,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B15">
-        <v>0.19995956122875211</v>
+        <v>0.1999595612287521</v>
       </c>
       <c r="C15">
-        <v>2.536307834088802E-2</v>
+        <v>0.02536307834088802</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1391,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>7.4167922139167786E-4</v>
+        <v>0.0007416792213916779</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1409,211 +1400,139 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B16">
-        <v>0.51009976863861084</v>
+        <v>0.5100997686386108</v>
       </c>
       <c r="C16">
-        <v>0.26117515563964838</v>
+        <v>0.2611751556396484</v>
       </c>
       <c r="D16">
-        <v>9.7866058349609375E-2</v>
+        <v>0.09786605834960938</v>
       </c>
       <c r="E16">
-        <v>5.9662342071533203E-2</v>
+        <v>0.0596623420715332</v>
       </c>
       <c r="F16">
-        <v>5.3807377815246582E-2</v>
+        <v>0.05380737781524658</v>
       </c>
       <c r="G16">
-        <v>4.8971652984619141E-2</v>
+        <v>0.04897165298461914</v>
       </c>
       <c r="H16">
-        <v>0.11905694007873539</v>
+        <v>0.1190569400787354</v>
       </c>
       <c r="I16">
-        <v>4.3361306190490723E-2</v>
+        <v>0.04336130619049072</v>
       </c>
       <c r="J16">
-        <v>4.017949104309082E-2</v>
+        <v>0.04017949104309082</v>
       </c>
       <c r="K16">
-        <v>3.8481712341308587E-2</v>
+        <v>0.03848171234130859</v>
       </c>
       <c r="L16">
-        <v>3.732454776763916E-2</v>
+        <v>0.03732454776763916</v>
       </c>
       <c r="M16">
-        <v>3.6690354347228997E-2</v>
-      </c>
-      <c r="N16">
-        <v>0.1260956525802612</v>
-      </c>
-      <c r="O16">
-        <v>7.5460076332092285E-2</v>
-      </c>
-      <c r="P16">
-        <v>3.2842397689819343E-2</v>
-      </c>
-      <c r="Q16">
-        <v>1.0657429695129389E-2</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>3.6919593811035163E-2</v>
-      </c>
-      <c r="U16">
-        <v>2.0824432373046878E-2</v>
-      </c>
-      <c r="V16">
-        <v>1.160180568695068E-2</v>
-      </c>
-      <c r="W16">
-        <v>4.111170768737793E-3</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.036690354347229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B17">
-        <v>2.842475101351738E-2</v>
+        <v>0.02842475101351738</v>
       </c>
       <c r="C17">
-        <v>1.531822886317968E-2</v>
+        <v>0.01531822886317968</v>
       </c>
       <c r="D17">
-        <v>7.4444045312702656E-3</v>
+        <v>0.007444404531270266</v>
       </c>
       <c r="E17">
-        <v>3.7815319374203682E-3</v>
+        <v>0.003781531937420368</v>
       </c>
       <c r="F17">
-        <v>2.8573651798069481E-3</v>
+        <v>0.002857365179806948</v>
       </c>
       <c r="G17">
-        <v>2.3938040249049659E-3</v>
+        <v>0.002393804024904966</v>
       </c>
       <c r="H17">
-        <v>5.6082597002387047E-3</v>
+        <v>0.005608259700238705</v>
       </c>
       <c r="I17">
-        <v>3.2615452073514462E-3</v>
+        <v>0.003261545207351446</v>
       </c>
       <c r="J17">
-        <v>2.5060386396944519E-3</v>
+        <v>0.002506038639694452</v>
       </c>
       <c r="K17">
-        <v>2.3457335773855452E-3</v>
+        <v>0.002345733577385545</v>
       </c>
       <c r="L17">
-        <v>2.2330703213810921E-3</v>
+        <v>0.002233070321381092</v>
       </c>
       <c r="M17">
-        <v>2.1642216015607119E-3</v>
-      </c>
-      <c r="N17">
-        <v>7.0124424993991852E-2</v>
-      </c>
-      <c r="O17">
-        <v>2.65833530575037E-2</v>
-      </c>
-      <c r="P17">
-        <v>1.0947465896606451E-2</v>
-      </c>
-      <c r="Q17">
-        <v>3.5524766426533461E-3</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>1.230653095990419E-2</v>
-      </c>
-      <c r="U17">
-        <v>6.9414773024618634E-3</v>
-      </c>
-      <c r="V17">
-        <v>3.867268562316895E-3</v>
-      </c>
-      <c r="W17">
-        <v>1.370390295051038E-3</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.002164221601560712</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B18">
-        <v>0.58817827701568604</v>
+        <v>0.09348547458648682</v>
       </c>
       <c r="C18">
-        <v>0.59260404109954834</v>
+        <v>0.07766544818878174</v>
       </c>
       <c r="D18">
-        <v>0.39067226648330688</v>
+        <v>0.06699740886688232</v>
       </c>
       <c r="E18">
-        <v>1.280486583709717E-3</v>
+        <v>0.0596623420715332</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>0.05380737781524658</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.04897165298461914</v>
       </c>
       <c r="H18">
-        <v>0.33498328924179083</v>
+        <v>0.04813659191131592</v>
       </c>
       <c r="I18">
-        <v>1.5682816505432129E-2</v>
+        <v>0.04336130619049072</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>0.04017949104309082</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>0.03848171234130859</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>0.03732454776763916</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>0.036690354347229</v>
       </c>
       <c r="N18">
-        <v>8.5137665271759033E-2</v>
+        <v>0.1065765619277954</v>
       </c>
       <c r="O18">
-        <v>5.2993118762969971E-2</v>
+        <v>0.06280362606048584</v>
       </c>
       <c r="P18">
-        <v>1.263755559921265E-2</v>
+        <v>0.02672731876373291</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>0.008203029632568359</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1622,16 +1541,16 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>0.03537571430206299</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>0.02073466777801514</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>0.01158559322357178</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>0.004111170768737793</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -1640,57 +1559,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B19">
-        <v>1.7438909038901329E-2</v>
+        <v>0.03372446820139885</v>
       </c>
       <c r="C19">
-        <v>1.3343449681997299E-2</v>
+        <v>0.0258884821087122</v>
       </c>
       <c r="D19">
-        <v>7.4575524777173996E-3</v>
+        <v>0.02233246900141239</v>
       </c>
       <c r="E19">
-        <v>2.2464677385869439E-5</v>
+        <v>0.01988744735717773</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.01793579198420048</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.0163238849490881</v>
       </c>
       <c r="H19">
-        <v>5.8768996968865386E-3</v>
+        <v>0.01604553125798702</v>
       </c>
       <c r="I19">
-        <v>2.7513713575899601E-4</v>
+        <v>0.01445376873016357</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>0.01339316368103027</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>0.01282723713666201</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>0.01244151592254639</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>0.01223011780530214</v>
       </c>
       <c r="N19">
-        <v>4.9534719437360757E-2</v>
+        <v>0.04736872389912605</v>
       </c>
       <c r="O19">
-        <v>2.0813902840018269E-2</v>
+        <v>0.02093454264104366</v>
       </c>
       <c r="P19">
-        <v>4.2125186882913113E-3</v>
+        <v>0.008909106254577637</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>0.002734343288466334</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1699,16 +1618,16 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.01179190445691347</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>0.006911555770784616</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>0.003861864330247045</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>0.001370390295051038</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -1717,239 +1636,557 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B20">
-        <v>0.58817827701568604</v>
+        <v>0.588178277015686</v>
       </c>
       <c r="C20">
-        <v>0.59260404109954834</v>
+        <v>0.5926040410995483</v>
       </c>
       <c r="D20">
-        <v>0.39067226648330688</v>
+        <v>0.3906722664833069</v>
       </c>
       <c r="E20">
-        <v>5.9662342071533203E-2</v>
+        <v>0.001280486583709717</v>
       </c>
       <c r="F20">
-        <v>5.3807377815246582E-2</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>4.8971652984619141E-2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>0.33498328924179083</v>
+        <v>0.3349832892417908</v>
       </c>
       <c r="I20">
-        <v>4.3361306190490723E-2</v>
+        <v>0.01568281650543213</v>
       </c>
       <c r="J20">
-        <v>4.017949104309082E-2</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>3.8481712341308587E-2</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>3.732454776763916E-2</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>3.6690354347228997E-2</v>
-      </c>
-      <c r="N20">
-        <v>0.1260956525802612</v>
-      </c>
-      <c r="O20">
-        <v>7.5460076332092285E-2</v>
-      </c>
-      <c r="P20">
-        <v>3.2842397689819343E-2</v>
-      </c>
-      <c r="Q20">
-        <v>1.0657429695129389E-2</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>3.6919593811035163E-2</v>
-      </c>
-      <c r="U20">
-        <v>2.0824432373046878E-2</v>
-      </c>
-      <c r="V20">
-        <v>1.160180568695068E-2</v>
-      </c>
-      <c r="W20">
-        <v>4.111170768737793E-3</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B21">
-        <v>2.2931830957531929E-2</v>
+        <v>0.01743890903890133</v>
       </c>
       <c r="C21">
-        <v>1.433083694428205E-2</v>
+        <v>0.0133434496819973</v>
       </c>
       <c r="D21">
-        <v>7.4509782716631889E-3</v>
+        <v>0.0074575524777174</v>
       </c>
       <c r="E21">
-        <v>1.9019983010366559E-3</v>
+        <v>2.246467738586944E-05</v>
       </c>
       <c r="F21">
-        <v>1.4286825899034741E-3</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>1.196902012452483E-3</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>5.7425796985626221E-3</v>
+        <v>0.005876899696886539</v>
       </c>
       <c r="I21">
-        <v>1.7683411715552211E-3</v>
+        <v>0.000275137135758996</v>
       </c>
       <c r="J21">
-        <v>1.2530193198472259E-3</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1.172866788692772E-3</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>1.116535160690546E-3</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>1.0821108007803559E-3</v>
-      </c>
-      <c r="N21">
-        <v>5.9829574078321457E-2</v>
-      </c>
-      <c r="O21">
-        <v>2.369862794876099E-2</v>
-      </c>
-      <c r="P21">
-        <v>7.5799920596182346E-3</v>
-      </c>
-      <c r="Q21">
-        <v>1.776238321326673E-3</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>6.1532654799520969E-3</v>
-      </c>
-      <c r="U21">
-        <v>3.4707386512309308E-3</v>
-      </c>
-      <c r="V21">
-        <v>1.933634281158447E-3</v>
-      </c>
-      <c r="W21">
-        <v>6.8519514752551913E-4</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B22">
-        <v>0.2322631627321243</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.23031140863895419</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0.22879080474376681</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>0.22776129841804499</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0.22695401310920721</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>0.22629259526729581</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0.22804614901542661</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0.22743633389472959</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>0.2270147502422333</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>0.22673626244068151</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>0.22653765976428991</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>0.22641158103942871</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0.04403406381607056</v>
+      </c>
+      <c r="O22">
+        <v>0.02253979444503784</v>
+      </c>
+      <c r="P22">
+        <v>0.0008146762847900391</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B23">
-        <v>0.22819787263870239</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0.2262762933969498</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0.22477875649929049</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0.22376599907875061</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0.2229725569486618</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>0.22232264280319211</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>0.2240479588508606</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0.2234475314617157</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>0.22303277254104609</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>0.22275885939598081</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>0.2225634753704071</v>
+        <v>0</v>
       </c>
       <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0.02232215739786625</v>
+      </c>
+      <c r="O23">
+        <v>0.007513264659792185</v>
+      </c>
+      <c r="P23">
+        <v>0.0002715587615966797</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>0.588178277015686</v>
+      </c>
+      <c r="C24">
+        <v>0.5926040410995483</v>
+      </c>
+      <c r="D24">
+        <v>0.3906722664833069</v>
+      </c>
+      <c r="E24">
+        <v>0.0596623420715332</v>
+      </c>
+      <c r="F24">
+        <v>0.05380737781524658</v>
+      </c>
+      <c r="G24">
+        <v>0.04897165298461914</v>
+      </c>
+      <c r="H24">
+        <v>0.3349832892417908</v>
+      </c>
+      <c r="I24">
+        <v>0.04336130619049072</v>
+      </c>
+      <c r="J24">
+        <v>0.04017949104309082</v>
+      </c>
+      <c r="K24">
+        <v>0.03848171234130859</v>
+      </c>
+      <c r="L24">
+        <v>0.03732454776763916</v>
+      </c>
+      <c r="M24">
+        <v>0.036690354347229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>0.02293183095753193</v>
+      </c>
+      <c r="C25">
+        <v>0.01433083694428205</v>
+      </c>
+      <c r="D25">
+        <v>0.007450978271663189</v>
+      </c>
+      <c r="E25">
+        <v>0.001901998301036656</v>
+      </c>
+      <c r="F25">
+        <v>0.001428682589903474</v>
+      </c>
+      <c r="G25">
+        <v>0.001196902012452483</v>
+      </c>
+      <c r="H25">
+        <v>0.005742579698562622</v>
+      </c>
+      <c r="I25">
+        <v>0.001768341171555221</v>
+      </c>
+      <c r="J25">
+        <v>0.001253019319847226</v>
+      </c>
+      <c r="K25">
+        <v>0.001172866788692772</v>
+      </c>
+      <c r="L25">
+        <v>0.001116535160690546</v>
+      </c>
+      <c r="M25">
+        <v>0.001082110800780356</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26">
+        <v>0.09348547458648682</v>
+      </c>
+      <c r="C26">
+        <v>0.07766544818878174</v>
+      </c>
+      <c r="D26">
+        <v>0.06699740886688232</v>
+      </c>
+      <c r="E26">
+        <v>0.0596623420715332</v>
+      </c>
+      <c r="F26">
+        <v>0.05380737781524658</v>
+      </c>
+      <c r="G26">
+        <v>0.04897165298461914</v>
+      </c>
+      <c r="H26">
+        <v>0.04813659191131592</v>
+      </c>
+      <c r="I26">
+        <v>0.04336130619049072</v>
+      </c>
+      <c r="J26">
+        <v>0.04017949104309082</v>
+      </c>
+      <c r="K26">
+        <v>0.03848171234130859</v>
+      </c>
+      <c r="L26">
+        <v>0.03732454776763916</v>
+      </c>
+      <c r="M26">
+        <v>0.036690354347229</v>
+      </c>
+      <c r="N26">
+        <v>0.1065765619277954</v>
+      </c>
+      <c r="O26">
+        <v>0.06280362606048584</v>
+      </c>
+      <c r="P26">
+        <v>0.02672731876373291</v>
+      </c>
+      <c r="Q26">
+        <v>0.008203029632568359</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0.03537571430206299</v>
+      </c>
+      <c r="U26">
+        <v>0.02073466777801514</v>
+      </c>
+      <c r="V26">
+        <v>0.01158559322357178</v>
+      </c>
+      <c r="W26">
+        <v>0.004111170768737793</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
+        <v>0.01686223410069942</v>
+      </c>
+      <c r="C27">
+        <v>0.0129442410543561</v>
+      </c>
+      <c r="D27">
+        <v>0.0111662345007062</v>
+      </c>
+      <c r="E27">
+        <v>0.009943723678588867</v>
+      </c>
+      <c r="F27">
+        <v>0.008967895992100239</v>
+      </c>
+      <c r="G27">
+        <v>0.008161942474544048</v>
+      </c>
+      <c r="H27">
+        <v>0.008022765628993511</v>
+      </c>
+      <c r="I27">
+        <v>0.007226884365081787</v>
+      </c>
+      <c r="J27">
+        <v>0.006696581840515137</v>
+      </c>
+      <c r="K27">
+        <v>0.006413618568331003</v>
+      </c>
+      <c r="L27">
+        <v>0.006220757961273193</v>
+      </c>
+      <c r="M27">
+        <v>0.006115058902651072</v>
+      </c>
+      <c r="N27">
+        <v>0.03484544157981873</v>
+      </c>
+      <c r="O27">
+        <v>0.01422390341758728</v>
+      </c>
+      <c r="P27">
+        <v>0.004590332508087158</v>
+      </c>
+      <c r="Q27">
+        <v>0.001367171644233167</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0.005895952228456736</v>
+      </c>
+      <c r="U27">
+        <v>0.003455777885392308</v>
+      </c>
+      <c r="V27">
+        <v>0.001930932165123522</v>
+      </c>
+      <c r="W27">
+        <v>0.0006851951475255191</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28">
+        <v>0.231054276227951</v>
+      </c>
+      <c r="C28">
+        <v>0.2297502160072327</v>
+      </c>
+      <c r="D28">
+        <v>0.228591576218605</v>
+      </c>
+      <c r="E28">
+        <v>0.2276681363582611</v>
+      </c>
+      <c r="F28">
+        <v>0.2269148677587509</v>
+      </c>
+      <c r="G28">
+        <v>0.2262925952672958</v>
+      </c>
+      <c r="H28">
+        <v>0.2277955561876297</v>
+      </c>
+      <c r="I28">
+        <v>0.2273163199424744</v>
+      </c>
+      <c r="J28">
+        <v>0.2269609570503235</v>
+      </c>
+      <c r="K28">
+        <v>0.226703867316246</v>
+      </c>
+      <c r="L28">
+        <v>0.2265219837427139</v>
+      </c>
+      <c r="M28">
+        <v>0.2264115810394287</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29">
+        <v>0.2270065993070602</v>
+      </c>
+      <c r="C29">
+        <v>0.2257221639156342</v>
+      </c>
+      <c r="D29">
+        <v>0.2245820313692093</v>
+      </c>
+      <c r="E29">
+        <v>0.2236743867397308</v>
+      </c>
+      <c r="F29">
+        <v>0.2229341417551041</v>
+      </c>
+      <c r="G29">
+        <v>0.2223226428031921</v>
+      </c>
+      <c r="H29">
+        <v>0.2238018363714218</v>
+      </c>
+      <c r="I29">
+        <v>0.223329558968544</v>
+      </c>
+      <c r="J29">
+        <v>0.2229799181222916</v>
+      </c>
+      <c r="K29">
+        <v>0.2227270901203156</v>
+      </c>
+      <c r="L29">
+        <v>0.2225481122732162</v>
+      </c>
+      <c r="M29">
         <v>0.2224394679069519</v>
       </c>
     </row>

--- a/verification/model_verification_results_57_buses_raw.xlsx
+++ b/verification/model_verification_results_57_buses_raw.xlsx
@@ -615,22 +615,22 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>1999999.75</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>2000009.25</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1999716.25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1999480.5</v>
+        <v>0.06859791278839111</v>
       </c>
       <c r="F2">
-        <v>1999352.375</v>
+        <v>0.1338188648223877</v>
       </c>
       <c r="G2">
-        <v>1999281.25</v>
+        <v>0.1642752289772034</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -651,40 +651,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>15.37712669372559</v>
+        <v>4.387126922607422</v>
       </c>
       <c r="O2">
-        <v>12.21967220306396</v>
+        <v>1.229672431945801</v>
       </c>
       <c r="P2">
-        <v>9.615761756896973</v>
+        <v>0.2735965847969055</v>
       </c>
       <c r="Q2">
-        <v>8.230090141296387</v>
+        <v>0.09311509132385254</v>
       </c>
       <c r="R2">
-        <v>7.434841632843018</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>6.880139827728271</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>9.584171295166016</v>
+        <v>0.5150699615478516</v>
       </c>
       <c r="U2">
-        <v>8.704327583312988</v>
+        <v>0.3344459533691406</v>
       </c>
       <c r="V2">
-        <v>8.140223503112793</v>
+        <v>0.1819635629653931</v>
       </c>
       <c r="W2">
-        <v>7.666530132293701</v>
+        <v>0.04992330074310303</v>
       </c>
       <c r="X2">
-        <v>7.249697208404541</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>6.875266075134277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -692,22 +692,22 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>1999356.625</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1998659.125</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1997902.375</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1997314.625</v>
+        <v>0.02286597155034542</v>
       </c>
       <c r="F3">
-        <v>1996980.375</v>
+        <v>0.0446062870323658</v>
       </c>
       <c r="G3">
-        <v>1996745.625</v>
+        <v>0.05475841090083122</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -728,40 +728,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.064881563186646</v>
+        <v>1.738559126853943</v>
       </c>
       <c r="O3">
-        <v>1.434581995010376</v>
+        <v>0.5873204469680786</v>
       </c>
       <c r="P3">
-        <v>0.9767890572547913</v>
+        <v>0.09119886159896851</v>
       </c>
       <c r="Q3">
-        <v>0.7578251361846924</v>
+        <v>0.03103836439549923</v>
       </c>
       <c r="R3">
-        <v>0.6395490169525146</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.5769748091697693</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.9818696975708008</v>
+        <v>0.1716899871826172</v>
       </c>
       <c r="U3">
-        <v>0.8356943726539612</v>
+        <v>0.1114819869399071</v>
       </c>
       <c r="V3">
-        <v>0.7439846396446228</v>
+        <v>0.06065452098846436</v>
       </c>
       <c r="W3">
-        <v>0.6682267189025879</v>
+        <v>0.01664110086858273</v>
       </c>
       <c r="X3">
-        <v>0.6184571385383606</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>0.5762704610824585</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -769,22 +769,22 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>1999902.5</v>
+        <v>0.9095296859741211</v>
       </c>
       <c r="C4">
-        <v>1999187.875</v>
+        <v>0.5250225067138672</v>
       </c>
       <c r="D4">
-        <v>1998845.625</v>
+        <v>0.1970243453979492</v>
       </c>
       <c r="E4">
-        <v>1998593.375</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1998464.5</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1998391.25</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -846,22 +846,22 @@
         <v>28</v>
       </c>
       <c r="B5">
-        <v>1999067</v>
+        <v>0.4043099582195282</v>
       </c>
       <c r="C5">
-        <v>1998243.125</v>
+        <v>0.1750075072050095</v>
       </c>
       <c r="D5">
-        <v>1997440.5</v>
+        <v>0.06567478179931641</v>
       </c>
       <c r="E5">
-        <v>1996785.625</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1996434.875</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1996186.375</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -882,37 +882,37 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.239311099052429</v>
+        <v>2.478622198104858</v>
       </c>
       <c r="O5">
-        <v>0.4933177530765533</v>
+        <v>0.9866355061531067</v>
       </c>
       <c r="P5">
-        <v>0.2585084438323975</v>
+        <v>0.5170168876647949</v>
       </c>
       <c r="Q5">
-        <v>0.08978640288114548</v>
+        <v>0.179572805762291</v>
       </c>
       <c r="R5">
-        <v>0.01926006935536861</v>
+        <v>0.03852013871073723</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0.2102902978658676</v>
+        <v>0.4205805957317352</v>
       </c>
       <c r="U5">
-        <v>0.1298189908266068</v>
+        <v>0.2596379816532135</v>
       </c>
       <c r="V5">
-        <v>0.07049701362848282</v>
+        <v>0.1409940272569656</v>
       </c>
       <c r="W5">
-        <v>0.03879138827323914</v>
+        <v>0.07758277654647827</v>
       </c>
       <c r="X5">
-        <v>0.01362917851656675</v>
+        <v>0.02725835703313351</v>
       </c>
       <c r="Y5">
         <v>0</v>
@@ -923,22 +923,22 @@
         <v>29</v>
       </c>
       <c r="B6">
-        <v>1999999.75</v>
+        <v>0.9095296859741211</v>
       </c>
       <c r="C6">
-        <v>2000009.25</v>
+        <v>0.5250225067138672</v>
       </c>
       <c r="D6">
-        <v>1999716.25</v>
+        <v>0.1970243453979492</v>
       </c>
       <c r="E6">
-        <v>1999480.5</v>
+        <v>0.06859791278839111</v>
       </c>
       <c r="F6">
-        <v>1999352.375</v>
+        <v>0.1338188648223877</v>
       </c>
       <c r="G6">
-        <v>1999281.25</v>
+        <v>0.1642752289772034</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -959,40 +959,40 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>15.37712669372559</v>
+        <v>4.387126922607422</v>
       </c>
       <c r="O6">
-        <v>12.21967220306396</v>
+        <v>2.693041324615479</v>
       </c>
       <c r="P6">
-        <v>9.615761756896973</v>
+        <v>1.383974432945251</v>
       </c>
       <c r="Q6">
-        <v>8.230090141296387</v>
+        <v>0.4997604489326477</v>
       </c>
       <c r="R6">
-        <v>7.434841632843018</v>
+        <v>0.1155604124069214</v>
       </c>
       <c r="S6">
-        <v>6.880139827728271</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>9.584171295166016</v>
+        <v>0.9952500462532043</v>
       </c>
       <c r="U6">
-        <v>8.704327583312988</v>
+        <v>0.6089640855789185</v>
       </c>
       <c r="V6">
-        <v>8.140223503112793</v>
+        <v>0.3991452157497406</v>
       </c>
       <c r="W6">
-        <v>7.666530132293701</v>
+        <v>0.2327483296394348</v>
       </c>
       <c r="X6">
-        <v>7.249697208404541</v>
+        <v>0.08177506923675537</v>
       </c>
       <c r="Y6">
-        <v>6.875266075134277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1000,22 +1000,22 @@
         <v>30</v>
       </c>
       <c r="B7">
-        <v>1999211.875</v>
+        <v>0.2021549791097641</v>
       </c>
       <c r="C7">
-        <v>1998451.125</v>
+        <v>0.08750375360250473</v>
       </c>
       <c r="D7">
-        <v>1997671.375</v>
+        <v>0.0328373908996582</v>
       </c>
       <c r="E7">
-        <v>1997050.125</v>
+        <v>0.01143298577517271</v>
       </c>
       <c r="F7">
-        <v>1996707.625</v>
+        <v>0.0223031435161829</v>
       </c>
       <c r="G7">
-        <v>1996466</v>
+        <v>0.02737920545041561</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1036,40 +1036,40 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.858489036560059</v>
+        <v>2.108590841293335</v>
       </c>
       <c r="O7">
-        <v>1.199265956878662</v>
+        <v>0.786978006362915</v>
       </c>
       <c r="P7">
-        <v>0.7972187995910645</v>
+        <v>0.3041078746318817</v>
       </c>
       <c r="Q7">
-        <v>0.5908154845237732</v>
+        <v>0.1053055822849274</v>
       </c>
       <c r="R7">
-        <v>0.4844768047332764</v>
+        <v>0.01926006935536861</v>
       </c>
       <c r="S7">
-        <v>0.4327311217784882</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.7889748215675354</v>
+        <v>0.296135276556015</v>
       </c>
       <c r="U7">
-        <v>0.6592255234718323</v>
+        <v>0.1855599880218506</v>
       </c>
       <c r="V7">
-        <v>0.5756127238273621</v>
+        <v>0.100824274122715</v>
       </c>
       <c r="W7">
-        <v>0.5108678936958313</v>
+        <v>0.04711193963885307</v>
       </c>
       <c r="X7">
-        <v>0.4672501385211945</v>
+        <v>0.01362917851656675</v>
       </c>
       <c r="Y7">
-        <v>0.4322028458118439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1077,22 +1077,22 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>1637.271728515625</v>
+        <v>3.936953783035278</v>
       </c>
       <c r="C8">
-        <v>1432.278564453125</v>
+        <v>3.550894975662231</v>
       </c>
       <c r="D8">
-        <v>1134.428955078125</v>
+        <v>3.232692956924438</v>
       </c>
       <c r="E8">
-        <v>870.9774169921875</v>
+        <v>2.983986616134644</v>
       </c>
       <c r="F8">
-        <v>784.3131713867188</v>
+        <v>2.750419855117798</v>
       </c>
       <c r="G8">
-        <v>721.5611572265625</v>
+        <v>2.52137303352356</v>
       </c>
       <c r="H8">
         <v>2.668367624282837</v>
@@ -1118,22 +1118,22 @@
         <v>32</v>
       </c>
       <c r="B9">
-        <v>879.480224609375</v>
+        <v>1.683251261711121</v>
       </c>
       <c r="C9">
-        <v>637.4147338867188</v>
+        <v>1.503276705741882</v>
       </c>
       <c r="D9">
-        <v>398.1282653808594</v>
+        <v>1.333090424537659</v>
       </c>
       <c r="E9">
-        <v>290.3258056640625</v>
+        <v>1.177107453346252</v>
       </c>
       <c r="F9">
-        <v>261.4377136230469</v>
+        <v>1.030398964881897</v>
       </c>
       <c r="G9">
-        <v>240.5203857421875</v>
+        <v>0.9043251872062683</v>
       </c>
       <c r="H9">
         <v>0.8982505798339844</v>
@@ -1159,22 +1159,22 @@
         <v>33</v>
       </c>
       <c r="B10">
-        <v>1262.382568359375</v>
+        <v>0.106132984161377</v>
       </c>
       <c r="C10">
-        <v>1107.089599609375</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>860.0577392578125</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>608.5933837890625</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>481.2086791992188</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>406.85888671875</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1200,22 +1200,22 @@
         <v>34</v>
       </c>
       <c r="B11">
-        <v>420.794189453125</v>
+        <v>0.03537766262888908</v>
       </c>
       <c r="C11">
-        <v>369.0298767089844</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>286.6859130859375</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>202.8644561767578</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>160.4028930664062</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>135.61962890625</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1241,22 +1241,22 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>1637.271728515625</v>
+        <v>3.936953783035278</v>
       </c>
       <c r="C12">
-        <v>1432.278564453125</v>
+        <v>3.550894975662231</v>
       </c>
       <c r="D12">
-        <v>1134.428955078125</v>
+        <v>3.232692956924438</v>
       </c>
       <c r="E12">
-        <v>870.9774169921875</v>
+        <v>2.983986616134644</v>
       </c>
       <c r="F12">
-        <v>784.3131713867188</v>
+        <v>2.750419855117798</v>
       </c>
       <c r="G12">
-        <v>721.5611572265625</v>
+        <v>2.52137303352356</v>
       </c>
       <c r="H12">
         <v>2.668367624282837</v>
@@ -1282,22 +1282,22 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>650.13720703125</v>
+        <v>0.8593144416809082</v>
       </c>
       <c r="C13">
-        <v>503.2222900390625</v>
+        <v>0.7516383528709412</v>
       </c>
       <c r="D13">
-        <v>342.4070739746094</v>
+        <v>0.6665452122688293</v>
       </c>
       <c r="E13">
-        <v>246.5951385498047</v>
+        <v>0.5885537266731262</v>
       </c>
       <c r="F13">
-        <v>210.9203033447266</v>
+        <v>0.5151994824409485</v>
       </c>
       <c r="G13">
-        <v>188.0700073242188</v>
+        <v>0.4521625936031342</v>
       </c>
       <c r="H13">
         <v>0.4491252899169922</v>
@@ -1600,16 +1600,16 @@
         <v>0.01223011780530214</v>
       </c>
       <c r="N19">
-        <v>0.04736872389912605</v>
+        <v>0.03856722638010979</v>
       </c>
       <c r="O19">
-        <v>0.02093454264104366</v>
+        <v>0.01332698296755552</v>
       </c>
       <c r="P19">
-        <v>0.008909106254577637</v>
+        <v>0.004454553127288818</v>
       </c>
       <c r="Q19">
-        <v>0.002734343288466334</v>
+        <v>0.001367171644233167</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1618,16 +1618,16 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0.01179190445691347</v>
+        <v>0.005895952228456736</v>
       </c>
       <c r="U19">
-        <v>0.006911555770784616</v>
+        <v>0.003455777885392308</v>
       </c>
       <c r="V19">
-        <v>0.003861864330247045</v>
+        <v>0.001930932165123522</v>
       </c>
       <c r="W19">
-        <v>0.001370390295051038</v>
+        <v>0.0006851951475255191</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>0.04403406381607056</v>
+        <v>0.04923784732818604</v>
       </c>
       <c r="O22">
         <v>0.02253979444503784</v>
@@ -1836,13 +1836,13 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0.02232215739786625</v>
+        <v>0.02892598509788513</v>
       </c>
       <c r="O23">
-        <v>0.007513264659792185</v>
+        <v>0.008031606674194336</v>
       </c>
       <c r="P23">
-        <v>0.0002715587615966797</v>
+        <v>0.0001357793807983398</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -2072,16 +2072,16 @@
         <v>0.006115058902651072</v>
       </c>
       <c r="N27">
-        <v>0.03484544157981873</v>
+        <v>0.03374660387635231</v>
       </c>
       <c r="O27">
-        <v>0.01422390341758728</v>
+        <v>0.01067929435521364</v>
       </c>
       <c r="P27">
-        <v>0.004590332508087158</v>
+        <v>0.002295166254043579</v>
       </c>
       <c r="Q27">
-        <v>0.001367171644233167</v>
+        <v>0.0006835858221165836</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2090,16 +2090,16 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>0.005895952228456736</v>
+        <v>0.002947976114228368</v>
       </c>
       <c r="U27">
-        <v>0.003455777885392308</v>
+        <v>0.001727888942696154</v>
       </c>
       <c r="V27">
-        <v>0.001930932165123522</v>
+        <v>0.0009654660825617611</v>
       </c>
       <c r="W27">
-        <v>0.0006851951475255191</v>
+        <v>0.0003425975737627596</v>
       </c>
       <c r="X27">
         <v>0</v>
